--- a/servo_calibrations.xlsx
+++ b/servo_calibrations.xlsx
@@ -1,49 +1,75 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\34618\Documents\GitHub\hex_esp32\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED223323-4DA0-4173-B1AD-FF68A28F8424}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E729F832-4C4C-4349-823A-7625588A62FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23148" yWindow="-72" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="6">
   <si>
     <t>servo</t>
   </si>
   <si>
-    <t>min(0)</t>
+    <t>-90</t>
   </si>
   <si>
-    <t>max(180)</t>
+    <t>0</t>
+  </si>
+  <si>
+    <t>90</t>
+  </si>
+  <si>
+    <t>*</t>
+  </si>
+  <si>
+    <t>Tocado</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -57,7 +83,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -65,12 +91,22 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -89,12 +125,14 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F5F9F69A-19A0-4A5C-924D-AE5B83EF8605}" name="Tabla1" displayName="Tabla1" ref="D5:F7" totalsRowShown="0">
-  <autoFilter ref="D5:F7" xr:uid="{F5F9F69A-19A0-4A5C-924D-AE5B83EF8605}"/>
-  <tableColumns count="3">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F5F9F69A-19A0-4A5C-924D-AE5B83EF8605}" name="Tabla1" displayName="Tabla1" ref="D5:H14" totalsRowShown="0">
+  <autoFilter ref="D5:H14" xr:uid="{F5F9F69A-19A0-4A5C-924D-AE5B83EF8605}"/>
+  <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{8CFD857D-17D9-47C1-BD3A-B16DAFA9416C}" name="servo"/>
-    <tableColumn id="2" xr3:uid="{12EEE1B6-3BBF-4964-95EB-1F94950541F6}" name="min(0)"/>
-    <tableColumn id="3" xr3:uid="{46E21357-50B1-40BC-AE3C-03C2D822F9E7}" name="max(180)"/>
+    <tableColumn id="2" xr3:uid="{12EEE1B6-3BBF-4964-95EB-1F94950541F6}" name="-90"/>
+    <tableColumn id="3" xr3:uid="{46E21357-50B1-40BC-AE3C-03C2D822F9E7}" name="0"/>
+    <tableColumn id="4" xr3:uid="{CB9F1111-7898-4819-BD0C-66618305BE8F}" name="90"/>
+    <tableColumn id="5" xr3:uid="{43A25DBC-B78B-4CD7-AA10-B457CE2718D7}" name="Tocado"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -363,13 +401,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="D5:F7"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="D5:H14"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="6" max="6" width="10.77734375" customWidth="1"/>
+    <col min="6" max="6" width="10.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D5" t="s">
         <v>0</v>
       </c>
@@ -379,24 +417,132 @@
       <c r="F5" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="6" spans="4:6" x14ac:dyDescent="0.3">
+      <c r="G5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D6">
         <v>0</v>
       </c>
       <c r="E6">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="F6">
-        <v>730</v>
-      </c>
-    </row>
-    <row r="7" spans="4:6" x14ac:dyDescent="0.3">
+        <v>350</v>
+      </c>
+      <c r="G6">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="7" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D7">
         <v>1</v>
       </c>
+      <c r="E7">
+        <v>230</v>
+      </c>
+      <c r="F7">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="8" spans="4:8" x14ac:dyDescent="0.25">
+      <c r="D8" s="1">
+        <v>2</v>
+      </c>
+      <c r="E8" s="1">
+        <v>250</v>
+      </c>
+      <c r="F8" s="1">
+        <v>480</v>
+      </c>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="4:8" x14ac:dyDescent="0.25">
+      <c r="D9">
+        <v>3</v>
+      </c>
+      <c r="E9">
+        <v>125</v>
+      </c>
+      <c r="F9">
+        <v>360</v>
+      </c>
+      <c r="G9">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="10" spans="4:8" x14ac:dyDescent="0.25">
+      <c r="D10">
+        <v>4</v>
+      </c>
+      <c r="E10">
+        <v>210</v>
+      </c>
+      <c r="F10">
+        <v>470</v>
+      </c>
+      <c r="H10" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="4:8" x14ac:dyDescent="0.25">
+      <c r="D11" s="1">
+        <v>5</v>
+      </c>
+      <c r="E11" s="1">
+        <v>210</v>
+      </c>
+      <c r="F11" s="1">
+        <v>450</v>
+      </c>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1"/>
+    </row>
+    <row r="12" spans="4:8" x14ac:dyDescent="0.25">
+      <c r="D12">
+        <v>6</v>
+      </c>
+      <c r="E12">
+        <v>130</v>
+      </c>
+      <c r="F12">
+        <v>375</v>
+      </c>
+      <c r="G12">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="13" spans="4:8" x14ac:dyDescent="0.25">
+      <c r="D13">
+        <v>7</v>
+      </c>
+      <c r="E13">
+        <v>240</v>
+      </c>
+      <c r="F13">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="14" spans="4:8" x14ac:dyDescent="0.25">
+      <c r="D14">
+        <v>8</v>
+      </c>
+      <c r="E14">
+        <v>200</v>
+      </c>
+      <c r="F14">
+        <v>460</v>
+      </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
